--- a/Solver/Solver.xlsx
+++ b/Solver/Solver.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Solver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7830D595-35B4-4035-9EEE-325F7F4DB7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187B65A4-BD32-4572-B0F5-5938D2BFCE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{02A40CC1-0F81-4A59-A5C9-979AEF35C4D8}"/>
   </bookViews>
@@ -20,6 +20,7 @@
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'Basic Solver'!$B$2:$B$5</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">'Max Solver'!$B$2:$B$4</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'Min Solver'!$B$4:$E$6</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
@@ -68,12 +69,13 @@
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">5</definedName>
-    <definedName name="solver_num" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">6</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'Basic Solver'!$D$6</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">'Max Solver'!$D$5</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'Min Solver'!$H$7</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -129,7 +131,7 @@
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">2000</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
@@ -156,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
   <si>
     <t>Particulars</t>
   </si>
@@ -366,6 +368,27 @@
   </si>
   <si>
     <t>it will change to integer.</t>
+  </si>
+  <si>
+    <t>sum of qt-1=b4 to b6</t>
+  </si>
+  <si>
+    <t>like this for qtr-2,3,4</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>Total Shipping Cost</t>
+  </si>
+  <si>
+    <t>calculate shipping cost</t>
   </si>
 </sst>
 </file>
@@ -485,8 +508,8 @@
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>487953</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>71187</xdr:rowOff>
     </xdr:to>
@@ -1169,15 +1192,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C39A8ECA-CC40-47D8-850C-B01AE5C61288}">
-  <dimension ref="A3:H8"/>
+  <dimension ref="A3:N23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>28</v>
@@ -1197,90 +1220,150 @@
       <c r="H3" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="L3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G4" s="1">
         <v>1.25</v>
       </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H4" s="1">
+        <f>SUM(B4:E4)*G4</f>
+        <v>395</v>
+      </c>
+      <c r="I4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4">
+        <v>20</v>
+      </c>
+      <c r="M4">
+        <v>72</v>
+      </c>
+      <c r="N4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1">
         <v>1.84</v>
       </c>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H5" s="1">
+        <f t="shared" ref="H5:H6" si="0">SUM(B5:E5)*G5</f>
+        <v>237.36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5">
+        <v>20</v>
+      </c>
+      <c r="M5">
+        <v>17</v>
+      </c>
+      <c r="N5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G6" s="1">
         <v>1.46</v>
       </c>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
+        <v>270.09999999999997</v>
+      </c>
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6">
+        <v>20</v>
+      </c>
+      <c r="M6">
+        <v>35</v>
+      </c>
+      <c r="N6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <f>SUM(B4:B6)</f>
+        <v>180</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <f t="shared" ref="C7:E7" si="1">SUM(C4:C6)</f>
+        <v>80</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>190</v>
       </c>
       <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="2">
+        <f>SUM(H4:H6)</f>
+        <v>902.46</v>
+      </c>
+      <c r="L7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -1298,6 +1381,35 @@
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
+      <c r="L8">
+        <f>180-60</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="L9">
+        <f>120-72</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="L10">
+        <f>48-35</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Solver/Solver.xlsx
+++ b/Solver/Solver.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Solver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187B65A4-BD32-4572-B0F5-5938D2BFCE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2F1ED1-3EB3-4196-9DF8-D6DC1B978B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{02A40CC1-0F81-4A59-A5C9-979AEF35C4D8}"/>
   </bookViews>
